--- a/dataset_t6_grouped/results2/G4/G4_T7486_W0023F0002T0006Z000C1N60_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T7486_W0023F0002T0006Z000C1N60_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>23.21040028433472</v>
+        <v>3.771690046204392</v>
       </c>
       <c r="D2" t="n">
-        <v>10.10703374672332</v>
+        <v>1.642392983842539</v>
       </c>
       <c r="E2" t="n">
-        <v>13.16355246340989</v>
+        <v>2.139077275304107</v>
       </c>
       <c r="F2" t="n">
-        <v>5.332229770175058</v>
+        <v>0.866487337653447</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>10.62126171026572</v>
+        <v>1.725955027918179</v>
       </c>
       <c r="D3" t="n">
-        <v>22.01750053769033</v>
+        <v>3.577843837374679</v>
       </c>
       <c r="E3" t="n">
-        <v>13.16355246340989</v>
+        <v>2.139077275304107</v>
       </c>
       <c r="F3" t="n">
-        <v>5.332229770175058</v>
+        <v>0.866487337653447</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>10.7131069796313</v>
+        <v>1.740879884190087</v>
       </c>
       <c r="D4" t="n">
-        <v>17.9277100449158</v>
+        <v>2.913252882298818</v>
       </c>
       <c r="E4" t="n">
-        <v>13.16355246340989</v>
+        <v>2.139077275304107</v>
       </c>
       <c r="F4" t="n">
-        <v>5.332229770175058</v>
+        <v>0.866487337653447</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>17.92179829992329</v>
+        <v>2.912292223737535</v>
       </c>
       <c r="D5" t="n">
-        <v>7.691395458746185</v>
+        <v>1.249851762046255</v>
       </c>
       <c r="E5" t="n">
-        <v>13.16355246340989</v>
+        <v>2.139077275304107</v>
       </c>
       <c r="F5" t="n">
-        <v>5.332229770175058</v>
+        <v>0.866487337653447</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>16.73362254084916</v>
+        <v>2.719213662887988</v>
       </c>
       <c r="D6" t="n">
-        <v>8.200449422862141</v>
+        <v>1.332573031215098</v>
       </c>
       <c r="E6" t="n">
-        <v>13.16355246340989</v>
+        <v>2.139077275304107</v>
       </c>
       <c r="F6" t="n">
-        <v>5.332229770175058</v>
+        <v>0.866487337653447</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>30.28577655463549</v>
+        <v>4.921438690128268</v>
       </c>
       <c r="D7" t="n">
-        <v>8.66719057009063</v>
+        <v>1.408418467639728</v>
       </c>
       <c r="E7" t="n">
-        <v>13.16355246340989</v>
+        <v>2.139077275304107</v>
       </c>
       <c r="F7" t="n">
-        <v>5.332229770175058</v>
+        <v>0.866487337653447</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>34.06690982591358</v>
+        <v>5.535872846710958</v>
       </c>
       <c r="D8" t="n">
-        <v>13.82839905615256</v>
+        <v>2.247114846624791</v>
       </c>
       <c r="E8" t="n">
-        <v>13.16355246340989</v>
+        <v>2.139077275304107</v>
       </c>
       <c r="F8" t="n">
-        <v>5.332229770175058</v>
+        <v>0.866487337653447</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>39.79969145482533</v>
+        <v>6.467449861409116</v>
       </c>
       <c r="D9" t="n">
-        <v>11.49844718543493</v>
+        <v>1.868497667633176</v>
       </c>
       <c r="E9" t="n">
-        <v>13.16355246340989</v>
+        <v>2.139077275304107</v>
       </c>
       <c r="F9" t="n">
-        <v>5.332229770175058</v>
+        <v>0.866487337653447</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>52.7766482078431</v>
+        <v>8.576205333774503</v>
       </c>
       <c r="D10" t="n">
-        <v>22.60814504160441</v>
+        <v>3.673823569260716</v>
       </c>
       <c r="E10" t="n">
-        <v>13.16355246340989</v>
+        <v>2.139077275304107</v>
       </c>
       <c r="F10" t="n">
-        <v>5.332229770175058</v>
+        <v>0.866487337653447</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>31.97765454936739</v>
+        <v>5.196368864272202</v>
       </c>
       <c r="D11" t="n">
-        <v>12.79592234574433</v>
+        <v>2.079337381183453</v>
       </c>
       <c r="E11" t="n">
-        <v>13.16355246340989</v>
+        <v>2.139077275304107</v>
       </c>
       <c r="F11" t="n">
-        <v>5.332229770175058</v>
+        <v>0.866487337653447</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>47.69660014962587</v>
+        <v>7.750697524314203</v>
       </c>
       <c r="D12" t="n">
-        <v>21.94061280802741</v>
+        <v>3.565349581304454</v>
       </c>
       <c r="E12" t="n">
-        <v>13.16355246340989</v>
+        <v>2.139077275304107</v>
       </c>
       <c r="F12" t="n">
-        <v>5.332229770175058</v>
+        <v>0.866487337653447</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>34.76922868060566</v>
+        <v>5.649999660598421</v>
       </c>
       <c r="D13" t="n">
-        <v>15.07074260863928</v>
+        <v>2.448995673903883</v>
       </c>
       <c r="E13" t="n">
-        <v>13.16355246340989</v>
+        <v>2.139077275304107</v>
       </c>
       <c r="F13" t="n">
-        <v>5.332229770175058</v>
+        <v>0.866487337653447</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
